--- a/ket_qua_K.xlsx
+++ b/ket_qua_K.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SAT K" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT K'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT K'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         <v>84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.00027</v>
+        <v>0.000405</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>7</v>
@@ -536,7 +536,7 @@
         <v>288</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.001474</v>
+        <v>0.001341</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>13</v>
@@ -563,7 +563,7 @@
         <v>740</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.004295</v>
+        <v>0.001948</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>21</v>
@@ -590,7 +590,7 @@
         <v>1590</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.017548</v>
+        <v>0.009387</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>31</v>
@@ -617,7 +617,7 @@
         <v>3024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.015771</v>
+        <v>0.007252</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>43</v>
@@ -644,7 +644,7 @@
         <v>5264</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.017098</v>
+        <v>0.017013</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>57</v>
@@ -671,7 +671,7 @@
         <v>8568</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.025262</v>
+        <v>0.041778</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>73</v>
@@ -698,7 +698,7 @@
         <v>13230</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.107531</v>
+        <v>0.05425</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>91</v>
@@ -725,7 +725,7 @@
         <v>19580</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.07595499999999999</v>
+        <v>0.092269</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>111</v>
@@ -752,7 +752,7 @@
         <v>27984</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.08125</v>
+        <v>0.10765</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>133</v>
@@ -763,8 +763,1034 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>K_13</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2041</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>38844</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.222278</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>K_14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2562</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>52598</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.202078</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>K_15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3165</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>69720</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.48126</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>K_16</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3856</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>90720</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.562096</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>K_17</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>4641</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>116144</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.557949</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>K_18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>5526</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>146574</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.828869</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>K_19</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>6517</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>182628</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1.530087</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>K_20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>7620</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>224960</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.794304</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>K_21</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>8841</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>274260</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1.229282</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>K_22</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>10186</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>331254</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1.813904</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>K_23</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>11661</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>396704</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1.949748</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>K_24</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>13272</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>471408</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2.444912</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>553</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>K_25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>15025</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>556200</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>3.961512</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>K_26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>16926</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>651950</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3.673556</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>651</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>K_27</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>18981</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>759564</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>5.671477</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>K_28</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>21196</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>879984</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>6.023303</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>K_29</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>23577</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1014188</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5.018656</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>K_30</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>26130</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1163190</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>5.528856</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>K_31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>28861</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1328040</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>7.509516</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>K_32</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>31776</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1509824</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>7.108919</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>993</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>K_33</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>34881</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1709664</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>12.451053</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1057</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>K_34</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>38182</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1928718</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>10.95266</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1123</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>K_35</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>41685</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2168180</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>14.596833</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1191</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>K_36</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>45396</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2429280</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>17.45216</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1261</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>K_37</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>49321</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2713284</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>20.620772</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>K_38</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>53466</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>3021494</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>15.818311</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>K_39</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>57837</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>3355248</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>18.006309</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1483</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>K_40</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>62440</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>3715920</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>25.265454</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1561</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>K_41</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>67281</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>4104920</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>22.626401</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1641</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>K_42</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>72366</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>4523694</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>25.224849</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1723</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>K_43</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>77701</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4973724</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>32.110126</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1807</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>K_44</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>5456528</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>44.302017</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>K_45</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>89145</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5973660</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>25.282856</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>K_46</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>95266</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>6526710</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>29.786667</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>K_47</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>101661</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>7117304</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>41.079829</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>2163</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>K_48</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>108336</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>7747104</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>35.030886</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>2257</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>K_49</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>115297</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>8417808</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>23.29158</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>2353</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>K_50</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>122550</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>9131150</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>28.263225</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>2451</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>